--- a/IFT_SafePredict_v1.0.xlsx
+++ b/IFT_SafePredict_v1.0.xlsx
@@ -53,15 +53,15 @@
     <definedName name="SC_x_CH4">'MARS_ENGINE'!$B$15</definedName>
     <definedName name="SC_x_N2">'MARS_ENGINE'!$B$16</definedName>
     <definedName name="SC_drho_sq">'MARS_ENGINE'!$B$17</definedName>
-    <definedName name="Sub_IFT">'MARS_ENGINE'!$B$33</definedName>
-    <definedName name="Sup_IFT">'MARS_ENGINE'!$B$68</definedName>
+    <definedName name="Sub_IFT">'MARS_ENGINE'!$B$34</definedName>
+    <definedName name="Sup_IFT">'MARS_ENGINE'!$B$70</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="238">
   <si>
     <t>IFT-SafePredict v1.0 — CO₂-Brine IFT Predictor</t>
   </si>
@@ -417,25 +417,31 @@
     <t>Sub term 12 (×+283.6242)</t>
   </si>
   <si>
-    <t>=+283.6242*(MAX(0,(-0.516)-SC_Tr)*MAX(0,SC_drho_sq-(0.0282)))</t>
-  </si>
-  <si>
-    <t>Sub term 13 (×-45.0736)</t>
-  </si>
-  <si>
-    <t>=-45.0736*(MAX(0,SC_Tr-(-0.8978))*MAX(0,(0.0282)-SC_drho_sq))</t>
-  </si>
-  <si>
-    <t>Sub term 14 (×+38.3241)</t>
-  </si>
-  <si>
-    <t>=+38.3241*(MAX(0,(-0.8978)-SC_Tr)*MAX(0,(0.0282)-SC_drho_sq))</t>
+    <t>=+283.6242*(MAX(0,(0.0282)-SC_drho_sq)*(2*ME_CH4_bin-1))</t>
+  </si>
+  <si>
+    <t>Sub term 13 (×-499.8016)</t>
+  </si>
+  <si>
+    <t>=-499.8016*(MAX(0,SC_Tr-(-0.8978))*MAX(0,(0.0282)-SC_drho_sq))</t>
+  </si>
+  <si>
+    <t>Sub term 14 (×-45.0736)</t>
+  </si>
+  <si>
+    <t>=-45.0736*(MAX(0,(-0.8978)-SC_Tr)*MAX(0,(0.0282)-SC_drho_sq))</t>
+  </si>
+  <si>
+    <t>Sub term 15 (×+38.3241)</t>
+  </si>
+  <si>
+    <t>=+38.3241*(MAX(0,(-0.3956)-SC_Tr)*SC_x_CH4)</t>
   </si>
   <si>
     <t>Sub IFT (mN/m)</t>
   </si>
   <si>
-    <t>=51.6236+MARS_ENGINE!B19+MARS_ENGINE!B20+MARS_ENGINE!B21+MARS_ENGINE!B22+MARS_ENGINE!B23+MARS_ENGINE!B24+MARS_ENGINE!B25+MARS_ENGINE!B26+MARS_ENGINE!B27+MARS_ENGINE!B28+MARS_ENGINE!B29+MARS_ENGINE!B30+MARS_ENGINE!B31+MARS_ENGINE!B32</t>
+    <t>=51.6236+MARS_ENGINE!B19+MARS_ENGINE!B20+MARS_ENGINE!B21+MARS_ENGINE!B22+MARS_ENGINE!B23+MARS_ENGINE!B24+MARS_ENGINE!B25+MARS_ENGINE!B26+MARS_ENGINE!B27+MARS_ENGINE!B28+MARS_ENGINE!B29+MARS_ENGINE!B30+MARS_ENGINE!B31+MARS_ENGINE!B32+MARS_ENGINE!B33</t>
   </si>
   <si>
     <t>§4 — Supercritical MARS (35-term) — used when regime = Supercritical</t>
@@ -444,205 +450,211 @@
     <t>Sup term 1 (×-59.8927)</t>
   </si>
   <si>
-    <t>=-59.8927*(MAX(0,SC_drho_sq-(0.4517)))</t>
+    <t>=-59.8927*(MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 2 (×+84.6131)</t>
   </si>
   <si>
-    <t>=+84.6131*(MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+84.6131*(MAX(0,SC_x_N2-(0.9652)))</t>
   </si>
   <si>
     <t>Sup term 3 (×-32.995)</t>
   </si>
   <si>
-    <t>=-32.995*(MAX(0,SC_x_N2-(0.9652)))</t>
+    <t>=-32.995*(MAX(0,(0.9652)-SC_x_N2))</t>
   </si>
   <si>
     <t>Sup term 4 (×-64.0876)</t>
   </si>
   <si>
-    <t>=-64.0876*(MAX(0,(0.9652)-SC_x_N2))</t>
+    <t>=-64.0876*(MAX(0,(0.7966)-SC_x_CH4))</t>
   </si>
   <si>
     <t>Sup term 5 (×+3.4684)</t>
   </si>
   <si>
-    <t>=+3.4684*(MAX(0,SC_x_CH4-(0.7966)))</t>
+    <t>=+3.4684*(MAX(0,SC_BCM-(-0.64))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 6 (×-8.4184)</t>
   </si>
   <si>
-    <t>=-8.4184*(MAX(0,(0.7966)-SC_x_CH4))</t>
+    <t>=-8.4184*(MAX(0,(-0.64)-SC_BCM)*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 7 (×-1959.2987)</t>
   </si>
   <si>
-    <t>=-1959.2987*(MAX(0,SC_BCM-(-0.64))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=-1959.2987*(MAX(0,SC_Tr-(-0.5087))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 8 (×+34.4304)</t>
   </si>
   <si>
-    <t>=+34.4304*(MAX(0,(-0.64)-SC_BCM)*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+34.4304*(MAX(0,(-0.5087)-SC_Tr)*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 9 (×+3.1914)</t>
   </si>
   <si>
-    <t>=+3.1914*(MAX(0,SC_Tr-(-0.5087))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+3.1914*(MAX(0,SC_MCM-(-0.802))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 10 (×-8.6816)</t>
   </si>
   <si>
-    <t>=-8.6816*(MAX(0,(-0.5087)-SC_Tr)*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=-8.6816*(MAX(0,(-0.802)-SC_MCM)*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 11 (×+4.235)</t>
   </si>
   <si>
-    <t>=+4.235*(MAX(0,SC_MCM-(-0.802))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+4.235*(MAX(0,SC_Tr-(-0.7733))*MAX(0,(0.9652)-SC_x_N2))</t>
   </si>
   <si>
     <t>Sup term 12 (×-29.5554)</t>
   </si>
   <si>
-    <t>=-29.5554*(MAX(0,(-0.802)-SC_MCM)*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=-29.5554*(MAX(0,(-0.7733)-SC_Tr)*MAX(0,(0.9652)-SC_x_N2))</t>
   </si>
   <si>
     <t>Sup term 13 (×+31.1754)</t>
   </si>
   <si>
-    <t>=+31.1754*(MAX(0,SC_Tr-(-0.7733))*MAX(0,(0.9652)-SC_x_N2))</t>
+    <t>=+31.1754*(MAX(0,SC_Tr-(-0.7165))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 14 (×+1733.7711)</t>
   </si>
   <si>
-    <t>=+1733.7711*(MAX(0,(-0.7733)-SC_Tr)*MAX(0,(0.9652)-SC_x_N2))</t>
+    <t>=+1733.7711*(MAX(0,SC_Tr-(-0.499))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 15 (×+302.2371)</t>
   </si>
   <si>
-    <t>=+302.2371*(MAX(0,SC_Tr-(-0.7165))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+302.2371*(MAX(0,SC_Tr-(-0.5359))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 16 (×+28.3565)</t>
   </si>
   <si>
-    <t>=+28.3565*(MAX(0,SC_Tr-(-0.499))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+28.3565*(MAX(0,(-0.9628)-SC_Pr)*MAX(0,(0.7966)-SC_x_CH4))</t>
   </si>
   <si>
     <t>Sup term 17 (×-136.4932)</t>
   </si>
   <si>
-    <t>=-136.4932*(MAX(0,SC_Tr-(-0.5359))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=-136.4932*(MAX(0,SC_Tr-(-0.437))*MAX(0,(0.4517)-SC_drho_sq))</t>
   </si>
   <si>
     <t>Sup term 18 (×-133.9788)</t>
   </si>
   <si>
-    <t>=-133.9788*(MAX(0,SC_Pr-(-0.9628))*MAX(0,(0.7966)-SC_x_CH4))</t>
+    <t>=-133.9788*(MAX(0,(0.7966)-SC_x_CH4)*MAX(0,SC_x_N2-(-0.3434)))</t>
   </si>
   <si>
     <t>Sup term 19 (×+126.0387)</t>
   </si>
   <si>
-    <t>=+126.0387*(MAX(0,(-0.9628)-SC_Pr)*MAX(0,(0.7966)-SC_x_CH4))</t>
+    <t>=+126.0387*(MAX(0,(0.7966)-SC_x_CH4)*MAX(0,SC_x_N2-(-0.3675)))</t>
   </si>
   <si>
     <t>Sup term 20 (×+8.6252)</t>
   </si>
   <si>
-    <t>=+8.6252*(MAX(0,SC_Tr-(-0.437))*MAX(0,(0.4517)-SC_drho_sq))</t>
+    <t>=+8.6252*(SC_BCM*MAX(0,SC_drho_sq-(0.4517)))</t>
   </si>
   <si>
     <t>Sup term 21 (×-13.5765)</t>
   </si>
   <si>
-    <t>=-13.5765*(MAX(0,(0.7966)-SC_x_CH4)*MAX(0,SC_x_N2-(-0.3434)))</t>
+    <t>=-13.5765*(MAX(0,SC_Pr-(-0.8438))*MAX(0,(0.9652)-SC_x_N2))</t>
   </si>
   <si>
     <t>Sup term 22 (×+21.9898)</t>
   </si>
   <si>
-    <t>=+21.9898*(MAX(0,(0.7966)-SC_x_CH4)*MAX(0,SC_x_N2-(-0.3675)))</t>
-  </si>
-  <si>
-    <t>Sup term 23 (×+24.6178)</t>
-  </si>
-  <si>
-    <t>=+24.6178*(MAX(0,SC_Pr-(-0.8438))*MAX(0,(0.9652)-SC_x_N2))</t>
-  </si>
-  <si>
-    <t>Sup term 24 (×+24.9711)</t>
-  </si>
-  <si>
-    <t>=+24.9711*(MAX(0,(-0.8438)-SC_Pr)*MAX(0,(0.9652)-SC_x_N2))</t>
-  </si>
-  <si>
-    <t>Sup term 25 (×-19.7154)</t>
-  </si>
-  <si>
-    <t>=-19.7154*(MAX(0,SC_x_N2-(0.2907))*MAX(0,(0.4517)-SC_drho_sq))</t>
-  </si>
-  <si>
-    <t>Sup term 26 (×+2.3966)</t>
-  </si>
-  <si>
-    <t>=+2.3966*(MAX(0,(0.2907)-SC_x_N2)*MAX(0,(0.4517)-SC_drho_sq))</t>
-  </si>
-  <si>
-    <t>Sup term 27 (×+68.834)</t>
-  </si>
-  <si>
-    <t>=+68.834*(MAX(0,SC_Pr-(-0.7159)))</t>
-  </si>
-  <si>
-    <t>Sup term 28 (×+3.7786)</t>
-  </si>
-  <si>
-    <t>=+3.7786*(MAX(0,(-0.7159)-SC_Pr))</t>
-  </si>
-  <si>
-    <t>Sup term 29 (×+5.372)</t>
-  </si>
-  <si>
-    <t>=+5.372*(MAX(0,SC_BCM-(-0.982))*MAX(0,(0.9652)-SC_x_N2))</t>
-  </si>
-  <si>
-    <t>Sup term 30 (×-31.8591)</t>
-  </si>
-  <si>
-    <t>=-31.8591*(MAX(0,(-0.982)-SC_BCM)*MAX(0,(0.9652)-SC_x_N2))</t>
-  </si>
-  <si>
-    <t>Sup term 31 (×+11.3604)</t>
-  </si>
-  <si>
-    <t>=+11.3604*(MAX(0,SC_Tr-(-0.3379))*MAX(0,(0.7966)-SC_x_CH4))</t>
-  </si>
-  <si>
-    <t>Sup term 32 (×+25.7311)</t>
-  </si>
-  <si>
-    <t>=+25.7311*(MAX(0,(-0.3379)-SC_Tr)*MAX(0,(0.7966)-SC_x_CH4))</t>
-  </si>
-  <si>
-    <t>Sup term 33 (×-133.2863)</t>
-  </si>
-  <si>
-    <t>=-133.2863*(MAX(0,SC_x_CH4-(-0.7551))*MAX(0,(0.9652)-SC_x_N2))</t>
+    <t>=+21.9898*(MAX(0,(-0.8438)-SC_Pr)*MAX(0,(0.9652)-SC_x_N2))</t>
+  </si>
+  <si>
+    <t>Sup term 23 (×-20.8103)</t>
+  </si>
+  <si>
+    <t>=-20.8103*(MAX(0,SC_x_N2-(0.2907))*MAX(0,(0.4517)-SC_drho_sq))</t>
+  </si>
+  <si>
+    <t>Sup term 24 (×+24.6178)</t>
+  </si>
+  <si>
+    <t>=+24.6178*(MAX(0,(0.2907)-SC_x_N2)*MAX(0,(0.4517)-SC_drho_sq))</t>
+  </si>
+  <si>
+    <t>Sup term 25 (×+24.9711)</t>
+  </si>
+  <si>
+    <t>=+24.9711*(MAX(0,SC_Pr-(-0.7159)))</t>
+  </si>
+  <si>
+    <t>Sup term 26 (×-19.7154)</t>
+  </si>
+  <si>
+    <t>=-19.7154*(MAX(0,(-0.7159)-SC_Pr))</t>
+  </si>
+  <si>
+    <t>Sup term 27 (×+2.3966)</t>
+  </si>
+  <si>
+    <t>=+2.3966*(MAX(0,SC_BCM-(-0.982))*MAX(0,(0.9652)-SC_x_N2))</t>
+  </si>
+  <si>
+    <t>Sup term 28 (×+68.834)</t>
+  </si>
+  <si>
+    <t>=+68.834*(MAX(0,(-0.982)-SC_BCM)*MAX(0,(0.9652)-SC_x_N2))</t>
+  </si>
+  <si>
+    <t>Sup term 29 (×+3.7786)</t>
+  </si>
+  <si>
+    <t>=+3.7786*(MAX(0,SC_Tr-(-0.3379))*MAX(0,(0.7966)-SC_x_CH4))</t>
+  </si>
+  <si>
+    <t>Sup term 30 (×+5.372)</t>
+  </si>
+  <si>
+    <t>=+5.372*(MAX(0,(-0.3379)-SC_Tr)*MAX(0,(0.7966)-SC_x_CH4))</t>
+  </si>
+  <si>
+    <t>Sup term 31 (×-31.8591)</t>
+  </si>
+  <si>
+    <t>=-31.8591*(MAX(0,SC_x_CH4-(-0.7551))*MAX(0,(0.9652)-SC_x_N2))</t>
+  </si>
+  <si>
+    <t>Sup term 32 (×+11.3604)</t>
+  </si>
+  <si>
+    <t>=+11.3604*(MAX(0,SC_x_CH4-(-0.5506))*MAX(0,(0.4517)-SC_drho_sq))</t>
+  </si>
+  <si>
+    <t>Sup term 33 (×+25.7311)</t>
+  </si>
+  <si>
+    <t>=+25.7311*(MAX(0,(-0.5506)-SC_x_CH4)*MAX(0,(0.4517)-SC_drho_sq))</t>
+  </si>
+  <si>
+    <t>Sup term 34 (×-133.2863)</t>
+  </si>
+  <si>
+    <t>=-133.2863*(MAX(0,(-0.7159)-SC_Pr)*MAX(0,(-0.9192)-SC_Tr))</t>
   </si>
   <si>
     <t>Sup IFT (mN/m)</t>
   </si>
   <si>
-    <t>=221.1467+MARS_ENGINE!B35+MARS_ENGINE!B36+MARS_ENGINE!B37+MARS_ENGINE!B38+MARS_ENGINE!B39+MARS_ENGINE!B40+MARS_ENGINE!B41+MARS_ENGINE!B42+MARS_ENGINE!B43+MARS_ENGINE!B44+MARS_ENGINE!B45+MARS_ENGINE!B46+MARS_ENGINE!B47+MARS_ENGINE!B48+MARS_ENGINE!B49+MARS_ENGINE!B50+MARS_ENGINE!B51+MARS_ENGINE!B52+MARS_ENGINE!B53+MARS_ENGINE!B54+MARS_ENGINE!B55+MARS_ENGINE!B56+MARS_ENGINE!B57+MARS_ENGINE!B58+MARS_ENGINE!B59+MARS_ENGINE!B60+MARS_ENGINE!B61+MARS_ENGINE!B62+MARS_ENGINE!B63+MARS_ENGINE!B64+MARS_ENGINE!B65+MARS_ENGINE!B66+MARS_ENGINE!B67</t>
+    <t>=221.1467+MARS_ENGINE!B36+MARS_ENGINE!B37+MARS_ENGINE!B38+MARS_ENGINE!B39+MARS_ENGINE!B40+MARS_ENGINE!B41+MARS_ENGINE!B42+MARS_ENGINE!B43+MARS_ENGINE!B44+MARS_ENGINE!B45+MARS_ENGINE!B46+MARS_ENGINE!B47+MARS_ENGINE!B48+MARS_ENGINE!B49+MARS_ENGINE!B50+MARS_ENGINE!B51+MARS_ENGINE!B52+MARS_ENGINE!B53+MARS_ENGINE!B54+MARS_ENGINE!B55+MARS_ENGINE!B56+MARS_ENGINE!B57+MARS_ENGINE!B58+MARS_ENGINE!B59+MARS_ENGINE!B60+MARS_ENGINE!B61+MARS_ENGINE!B62+MARS_ENGINE!B63+MARS_ENGINE!B64+MARS_ENGINE!B65+MARS_ENGINE!B66+MARS_ENGINE!B67+MARS_ENGINE!B68+MARS_ENGINE!B69</t>
   </si>
   <si>
     <t>Feature</t>
@@ -735,7 +747,7 @@
     <t>Dataset    : 3,265 CO₂-Brine IFT measurements (1,400 subcritical + 1,865 supercritical), 16 laboratories.</t>
   </si>
   <si>
-    <t>Subcritical: MARS 16-term (compliance-fixed). Test nRMSE=5.95%, R²=0.939. Features: Pr, Tr, Δρ², x_CH₄, CH4_bin.</t>
+    <t>Subcritical: MARS 16-term (compliance-fixed). Test nRMSE=5.46%, R²=0.939. Features: Pr, Tr, Δρ², x_CH₄, CH4_bin.</t>
   </si>
   <si>
     <t>Supercritical: MARS 35-term. Test nRMSE=5.60%, R²=0.928. Features: all 10 (Pr,Tr,MCM,BCM,x_CH₄,x_N₂,Δρ²,BCM_bin,CH4_bin,N2_bin).</t>
@@ -1752,7 +1764,7 @@
   <sheetPr>
     <tabColor rgb="FF475569"/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2010,26 +2022,26 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+      <c r="A33" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="22" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="20"/>
+      <c r="B34" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="22" t="s">
+      <c r="A35" s="20" t="s">
         <v>127</v>
       </c>
+      <c r="B35" s="20"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -2288,11 +2300,27 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="23" t="s">
+      <c r="A68" t="s">
         <v>192</v>
       </c>
-      <c r="B68" s="23" t="s">
+      <c r="B68" s="22" t="s">
         <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>194</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2300,7 +2328,7 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2321,19 +2349,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2347,10 +2375,10 @@
         <v>4.694600993224932</v>
       </c>
       <c r="D2" s="24">
-        <v>1.011</v>
+        <v>1.0027100271002711</v>
       </c>
       <c r="E2" s="24">
-        <v>4.457</v>
+        <v>9.418699186991873</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2364,15 +2392,15 @@
         <v>2.217196589822707</v>
       </c>
       <c r="D3" s="25">
-        <v>1.002</v>
+        <v>1.0125542263704483</v>
       </c>
       <c r="E3" s="25">
-        <v>1.258</v>
+        <v>2.2171965898227066</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B4" s="24">
         <v>0</v>
@@ -2384,12 +2412,12 @@
         <v>0</v>
       </c>
       <c r="E4" s="24">
-        <v>4.88</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B5" s="25">
         <v>0</v>
@@ -2401,12 +2429,12 @@
         <v>0</v>
       </c>
       <c r="E5" s="25">
-        <v>1.48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B6" s="24">
         <v>0</v>
@@ -2418,12 +2446,12 @@
         <v>0</v>
       </c>
       <c r="E6" s="24">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B7" s="25">
         <v>0</v>
@@ -2435,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="25">
-        <v>0.15</v>
+        <v>0.7636</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2449,10 +2477,10 @@
         <v>1.294887038140309</v>
       </c>
       <c r="D8" s="24">
-        <v>0.001</v>
+        <v>0.001681</v>
       </c>
       <c r="E8" s="24">
-        <v>0.198</v>
+        <v>1.6030851769</v>
       </c>
     </row>
   </sheetData>
@@ -2474,157 +2502,157 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/IFT_SafePredict_v1.0.xlsx
+++ b/IFT_SafePredict_v1.0.xlsx
@@ -165,7 +165,7 @@
     <t>Tc_mix (K)</t>
   </si>
   <si>
-    <t>=B7*190.56+B8*126.19+(1-B7-B8)*304.13</t>
+    <t>=B7*190.56+B8*126.19+(1-B7-B8)*304.28</t>
   </si>
   <si>
     <t>Pr</t>
@@ -231,7 +231,7 @@
     <t>IFT P10 — 80% CI lower (mN/m)</t>
   </si>
   <si>
-    <t>=MAX(12.4,B23-(IF(B20="Subcritical",2.44,2.25))*B24)</t>
+    <t>=MAX(12.4,B23-(IF(B20="Subcritical",2.6928,2.25))*B24)</t>
   </si>
   <si>
     <t>80% conformal lower bound</t>
@@ -240,7 +240,7 @@
     <t>IFT P90 — 80% CI upper (mN/m)</t>
   </si>
   <si>
-    <t>=MIN(78.88,B23+(IF(B20="Subcritical",2.44,2.25))*B24)</t>
+    <t>=MIN(78.88,B23+(IF(B20="Subcritical",2.6928,2.25))*B24)</t>
   </si>
   <si>
     <t>80% conformal upper bound</t>
@@ -267,7 +267,7 @@
     <t>=INPUT!B7*4.6 + INPUT!B8*3.39 + (1-INPUT!B7-INPUT!B8)*7.377</t>
   </si>
   <si>
-    <t>=INPUT!B7*190.56 + INPUT!B8*126.19 + (1-INPUT!B7-INPUT!B8)*304.13</t>
+    <t>=INPUT!B7*190.56 + INPUT!B8*126.19 + (1-INPUT!B7-INPUT!B8)*304.28</t>
   </si>
   <si>
     <t>=INPUT!B2/MARS_ENGINE!B3</t>
@@ -735,7 +735,7 @@
     <t>GREEN ✓   : Input within validated training domain. Standard uncertainty (UIF=1.0).</t>
   </si>
   <si>
-    <t>YELLOW ⚠  : Na₂SO₄ brine or MCM &gt; 2.5 mol/kg. Li et al. (2012) apparatus offset (+11%). UIF=3.41.</t>
+    <t>YELLOW ⚠  : Na₂SO₄ brine or MCM &gt; 2.5 mol/kg. Li et al. (2012) apparatus offset (+13.51%). UIF=3.41.</t>
   </si>
   <si>
     <t>RED ⚠     : One or more inputs outside training domain bounds. Extrapolation. UIF=5.0. Use with caution.</t>
@@ -747,13 +747,13 @@
     <t>Dataset    : 3,265 CO₂-Brine IFT measurements (1,400 subcritical + 1,865 supercritical), 16 laboratories.</t>
   </si>
   <si>
-    <t>Subcritical: MARS 16-term (compliance-fixed). Test nRMSE=5.46%, R²=0.939. Features: Pr, Tr, Δρ², x_CH₄, CH4_bin.</t>
+    <t>Subcritical: MARS 16-term (compliance-fixed). Test nRMSE=5.95%, R²=0.939. Features: Pr, Tr, Δρ², x_CH₄, CH4_bin.</t>
   </si>
   <si>
     <t>Supercritical: MARS 35-term. Test nRMSE=5.60%, R²=0.928. Features: all 10 (Pr,Tr,MCM,BCM,x_CH₄,x_N₂,Δρ²,BCM_bin,CH4_bin,N2_bin).</t>
   </si>
   <si>
-    <t>UQ: 80% conformal prediction intervals. Base half-width ±2.44 mN/m (sub), ±2.25 mN/m (sup).</t>
+    <t>UQ: 80% conformal prediction intervals. Base half-width ±2.6928 mN/m (sub), ±2.25 mN/m (sup).</t>
   </si>
   <si>
     <t>P10/P90 clamped at physical limits: floor 12.4 mN/m, cap 78.88 mN/m.</t>
@@ -762,10 +762,10 @@
     <t>§5  Citation</t>
   </si>
   <si>
-    <t>Olagunju, D. et al. (2026). CO₂-Brine Interfacial Tension Prediction via Dual-Regime MARS Models</t>
-  </si>
-  <si>
-    <t>with Conformal Uncertainty Quantification. [Journal TBD].</t>
+    <t>Olagunju, D. et al. (2026). Closed-Form MARS Equations with Calibrated Conformal Uncertainty for</t>
+  </si>
+  <si>
+    <t>CO₂-Brine Interfacial Tension Prediction in Geological Carbon Storage.</t>
   </si>
   <si>
     <t>§6  Disclaimer</t>
